--- a/gold_port_plan.xlsx
+++ b/gold_port_plan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/defnehiz/API_Extraction_DMATL-1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A41E10A-BF37-EA40-AB60-65BA1951A749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{723D9D9A-FAD0-5C44-AE39-25B5F49114DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17240" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="changes" sheetId="1" r:id="rId1"/>
@@ -648,7 +648,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -671,14 +671,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -686,14 +705,148 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -704,6 +857,23 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D20102A7-0DE5-3241-B963-7FEDED910E58}" name="Table1" displayName="Table1" ref="A1:H79" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" headerRowBorderDxfId="10" tableBorderDxfId="11">
+  <autoFilter ref="A1:H79" xr:uid="{D20102A7-0DE5-3241-B963-7FEDED910E58}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{4015A5E7-9DDC-4448-86BC-A5139ED6460F}" name="sheet" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{0E0BE8D3-23EA-BA4A-B744-6E35F029D617}" name="record_id" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{5ADFCD3B-8DB8-C946-AC1B-4654986B617A}" name="material_name" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{A9AA0247-C71F-8E43-B890-DE2557D2D997}" name="column" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{69C110A6-7D5A-C34F-9D1C-49D65B91FDB1}" name="current_new_value" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{8D985E69-C0F8-F549-801E-A114C6ED173D}" name="incoming_old_value" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{2B168653-D694-BB42-9B83-B330D76B9883}" name="kind" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{1C528557-1BD1-9842-BFA4-2B5AEDBAB067}" name="matched_by" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -994,1876 +1164,1884 @@
   <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="26.1640625" defaultRowHeight="34" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.1640625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="52" style="2" customWidth="1"/>
-    <col min="3" max="3" width="26.1640625" style="2"/>
-    <col min="4" max="4" width="29" style="2" customWidth="1"/>
-    <col min="5" max="5" width="42.5" style="2" customWidth="1"/>
-    <col min="6" max="6" width="78.1640625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="26.1640625" style="2"/>
+    <col min="1" max="1" width="26.1640625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="52" style="4" customWidth="1"/>
+    <col min="3" max="3" width="26.1640625" style="4"/>
+    <col min="4" max="4" width="29" style="4" customWidth="1"/>
+    <col min="5" max="5" width="42.5" style="4" customWidth="1"/>
+    <col min="6" max="6" width="78.1640625" style="4" customWidth="1"/>
+    <col min="7" max="16384" width="26.1640625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:8" s="6" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="3" t="s">
+    <row r="2" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="F2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="F3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="F4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="F5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="F6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="3" t="s">
+      <c r="F7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="s">
+      <c r="G8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="3" t="s">
+      <c r="F9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="3" t="s">
+      <c r="F10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="3" t="s">
+      <c r="F11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="3" t="s">
+      <c r="F12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F13" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="3" t="s">
+      <c r="F13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="3" t="s">
+      <c r="G14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="3" t="s">
+      <c r="F15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" s="3" t="s">
+      <c r="F16" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" s="3" t="s">
+      <c r="F17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" s="3" t="s">
+      <c r="F18" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F19" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" s="3" t="s">
+      <c r="F19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" s="3" t="s">
+      <c r="F20" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" s="3" t="s">
+      <c r="F21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="3" t="s">
+      <c r="F22" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" s="3" t="s">
+      <c r="F23" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25" s="3" t="s">
+      <c r="F24" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F25" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" s="3" t="s">
+      <c r="F25" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="F26" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B27" s="3" t="s">
+      <c r="G26" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F27" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B28" s="3" t="s">
+      <c r="F27" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F28" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B29" s="3" t="s">
+      <c r="F28" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F29" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B30" s="3" t="s">
+      <c r="F29" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D30" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F30" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B31" s="3" t="s">
+      <c r="F30" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D31" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F31" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B32" s="3" t="s">
+      <c r="F31" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B33" s="3" t="s">
+      <c r="F32" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D33" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B34" s="3" t="s">
+      <c r="F33" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D34" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F34" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B35" s="3" t="s">
+      <c r="F34" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B36" s="3" t="s">
+      <c r="F35" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B36" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D36" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F36" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B37" s="3" t="s">
+      <c r="F36" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B37" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="D37" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F37" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B38" s="3" t="s">
+      <c r="F37" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D38" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F38" s="3" t="s">
+      <c r="F38" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B39" s="3" t="s">
+      <c r="G38" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B39" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D39" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F39" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B40" s="3" t="s">
+      <c r="F39" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B40" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="D40" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F40" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B41" s="3" t="s">
+      <c r="F40" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B41" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="D41" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B42" s="3" t="s">
+      <c r="F41" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B42" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="D42" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F42" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B43" s="3" t="s">
+      <c r="F42" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B43" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="D43" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B44" s="3" t="s">
+      <c r="F43" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B44" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C44" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="D44" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B45" s="3" t="s">
+      <c r="F44" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B45" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C45" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D45" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B46" s="3" t="s">
+      <c r="F45" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B46" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C46" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="D46" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B47" s="3" t="s">
+      <c r="F46" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H46" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B47" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D47" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B48" s="3" t="s">
+      <c r="F47" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H47" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B48" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C48" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="D48" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B49" s="3" t="s">
+      <c r="F48" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H48" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B49" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C49" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="D49" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B50" s="3" t="s">
+      <c r="F49" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H49" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B50" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C50" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D50" s="3" t="s">
+      <c r="D50" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F50" s="3" t="s">
+      <c r="F50" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G50" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B51" s="3" t="s">
+      <c r="G50" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H50" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B51" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C51" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="D51" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F51" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B52" s="3" t="s">
+      <c r="F51" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B52" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C52" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="D52" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B53" s="3" t="s">
+      <c r="F52" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H52" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B53" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C53" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="D53" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E53" s="3" t="s">
+      <c r="E53" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="F53" s="3" t="s">
+      <c r="F53" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="G53" s="3" t="s">
+      <c r="G53" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="H53" s="3" t="s">
+      <c r="H53" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B54" s="2" t="s">
+      <c r="A54" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B54" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="D54" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E54" s="2">
+      <c r="E54" s="4">
         <v>2.0499999999999998</v>
       </c>
-      <c r="F54" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G54" s="2" t="s">
+      <c r="F54" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G54" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="H54" s="2" t="s">
+      <c r="H54" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B55" s="2" t="s">
+      <c r="A55" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B55" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="D55" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E55" s="2" t="s">
+      <c r="E55" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="F55" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G55" s="2" t="s">
+      <c r="F55" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G55" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="H55" s="2" t="s">
+      <c r="H55" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B56" s="2" t="s">
+      <c r="A56" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B56" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="D56" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E56" s="2">
+      <c r="E56" s="4">
         <v>0.6</v>
       </c>
-      <c r="F56" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G56" s="2" t="s">
+      <c r="F56" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G56" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="H56" s="2" t="s">
+      <c r="H56" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B57" s="2" t="s">
+      <c r="A57" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B57" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="D57" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E57" s="2" t="s">
+      <c r="E57" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="F57" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G57" s="2" t="s">
+      <c r="F57" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G57" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="H57" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B58" s="3" t="s">
+      <c r="H57" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B58" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C58" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D58" s="3" t="s">
+      <c r="D58" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B59" s="3" t="s">
+      <c r="F58" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H58" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B59" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C59" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="D59" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B60" s="3" t="s">
+      <c r="F59" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H59" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B60" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C60" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="3" t="s">
+      <c r="D60" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B61" s="3" t="s">
+      <c r="F60" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H60" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B61" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="C61" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D61" s="3" t="s">
+      <c r="D61" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F61" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B62" s="3" t="s">
+      <c r="F61" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H61" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B62" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="C62" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="3" t="s">
+      <c r="D62" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F62" s="3" t="s">
+      <c r="F62" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B63" s="3" t="s">
+      <c r="G62" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H62" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B63" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="C63" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D63" s="3" t="s">
+      <c r="D63" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F63" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H63" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B64" s="3" t="s">
+      <c r="F63" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H63" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B64" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C64" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D64" s="3" t="s">
+      <c r="D64" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F64" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B65" s="3" t="s">
+      <c r="F64" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H64" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B65" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="C65" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D65" s="3" t="s">
+      <c r="D65" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E65" s="3" t="s">
+      <c r="E65" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F65" s="3" t="s">
+      <c r="F65" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="G65" s="3" t="s">
+      <c r="G65" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="H65" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B66" s="3" t="s">
+      <c r="H65" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B66" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="C66" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D66" s="3" t="s">
+      <c r="D66" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E66" s="3" t="s">
+      <c r="E66" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="F66" s="3" t="s">
+      <c r="F66" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="G66" s="3" t="s">
+      <c r="G66" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B67" s="3" t="s">
+      <c r="H66" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B67" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C67" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="D67" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E67" s="3" t="s">
+      <c r="E67" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="F67" s="3" t="s">
+      <c r="F67" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="G67" s="3" t="s">
+      <c r="G67" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="H67" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B68" s="3" t="s">
+      <c r="H67" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B68" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="C68" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D68" s="3" t="s">
+      <c r="D68" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F68" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B69" s="3" t="s">
+      <c r="F68" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H68" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B69" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="C69" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D69" s="3" t="s">
+      <c r="D69" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F69" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B70" s="3" t="s">
+      <c r="F69" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G69" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H69" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B70" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C70" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="D70" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E70" s="3" t="s">
+      <c r="E70" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F70" s="3" t="s">
+      <c r="F70" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="G70" s="3" t="s">
+      <c r="G70" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="H70" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B71" s="3" t="s">
+      <c r="H70" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B71" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="C71" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="D71" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F71" s="3" t="s">
+      <c r="F71" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="G71" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H71" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B72" s="3" t="s">
+      <c r="G71" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H71" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B72" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="C72" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="D72" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F72" s="3" t="s">
+      <c r="F72" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B73" s="3" t="s">
+      <c r="G72" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H72" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B73" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="C73" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D73" s="3" t="s">
+      <c r="D73" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F73" s="3" t="s">
+      <c r="F73" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="G73" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H73" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B74" s="3" t="s">
+      <c r="G73" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H73" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B74" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="C74" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D74" s="3" t="s">
+      <c r="D74" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F74" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G74" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="3" t="s">
+      <c r="F74" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G74" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H74" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="B75" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="C75" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D75" s="3" t="s">
+      <c r="D75" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="F75" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H75" s="3" t="s">
+      <c r="F75" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G75" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H75" s="5" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="3" t="s">
+    <row r="76" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="B76" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="C76" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D76" s="3" t="s">
+      <c r="D76" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="F76" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H76" s="3" t="s">
+      <c r="F76" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H76" s="5" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="2" t="s">
+      <c r="A77" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="B77" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="C77" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D77" s="2" t="s">
+      <c r="D77" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E77" s="2">
+      <c r="E77" s="4">
         <v>293</v>
       </c>
-      <c r="F77" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G77" s="2" t="s">
+      <c r="F77" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G77" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="H77" s="2" t="s">
+      <c r="H77" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="78" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="3" t="s">
+    <row r="78" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="B78" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="C78" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D78" s="3" t="s">
+      <c r="D78" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F78" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G78" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H78" s="3" t="s">
+      <c r="F78" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G78" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H78" s="5" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="79" spans="1:8" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="3" t="s">
+    <row r="79" spans="1:8" s="5" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B79" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C79" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D79" s="3" t="s">
+      <c r="D79" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="F79" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G79" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H79" s="3" t="s">
+      <c r="F79" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G79" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H79" s="5" t="s">
         <v>66</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F65"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="17.33203125" defaultRowHeight="97" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="5" width="17.33203125" style="4"/>
+    <col min="6" max="6" width="104.1640625" style="4" customWidth="1"/>
+    <col min="7" max="16384" width="17.33203125" style="4"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2883,1163 +3061,1163 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="2" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="D2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="3" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="E3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="E3" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="4" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="E4" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="5" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E5" t="s">
-        <v>76</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="E5" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
+    <row r="6" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E6" t="s">
-        <v>76</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="E6" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
+    <row r="7" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E7" t="s">
-        <v>76</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="E7" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
+    <row r="8" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E8" t="s">
-        <v>76</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="E8" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
+    <row r="9" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E9" t="s">
-        <v>76</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="E9" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
+    <row r="10" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E10" t="s">
-        <v>76</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="E10" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" t="s">
+    <row r="11" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E11" t="s">
-        <v>76</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="E11" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" t="s">
+    <row r="12" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E12" t="s">
-        <v>76</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="E12" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" t="s">
+    <row r="13" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="E13" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" t="s">
+    <row r="14" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="E14" t="s">
-        <v>76</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="E14" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" t="s">
+    <row r="15" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="E15" t="s">
-        <v>76</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="E15" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" t="s">
+    <row r="16" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E16" t="s">
-        <v>76</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="E16" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+    <row r="17" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="E17" t="s">
-        <v>76</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="E17" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
+    <row r="18" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="E18" t="s">
-        <v>76</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="E18" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
+    <row r="19" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="E19" t="s">
-        <v>76</v>
-      </c>
-      <c r="F19" t="s">
+      <c r="E19" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+    <row r="20" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="E20" t="s">
-        <v>76</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="E20" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
+    <row r="21" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="E21" t="s">
-        <v>76</v>
-      </c>
-      <c r="F21" t="s">
+      <c r="E21" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+    <row r="22" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E22" t="s">
-        <v>76</v>
-      </c>
-      <c r="F22" t="s">
+      <c r="E22" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F22" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+    <row r="23" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E23" t="s">
-        <v>76</v>
-      </c>
-      <c r="F23" t="s">
+      <c r="E23" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F23" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+    <row r="24" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="E24" t="s">
-        <v>76</v>
-      </c>
-      <c r="F24" t="s">
+      <c r="E24" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F24" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+    <row r="25" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="E25" t="s">
-        <v>76</v>
-      </c>
-      <c r="F25" t="s">
+      <c r="E25" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F25" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+    <row r="26" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="E26" t="s">
-        <v>76</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="E26" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F26" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
+    <row r="27" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="E27" t="s">
-        <v>76</v>
-      </c>
-      <c r="F27" t="s">
+      <c r="E27" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F27" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
+    <row r="28" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="E28" t="s">
-        <v>76</v>
-      </c>
-      <c r="F28" t="s">
+      <c r="E28" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F28" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
+    <row r="29" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="E29" t="s">
-        <v>76</v>
-      </c>
-      <c r="F29" t="s">
+      <c r="E29" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F29" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
+    <row r="30" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="E30" t="s">
-        <v>76</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="E30" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F30" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
+    <row r="31" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="E31" t="s">
-        <v>76</v>
-      </c>
-      <c r="F31" t="s">
+      <c r="E31" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
+    <row r="32" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="E32" t="s">
-        <v>76</v>
-      </c>
-      <c r="F32" t="s">
+      <c r="E32" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F32" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
+    <row r="33" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="E33" t="s">
-        <v>76</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="E33" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F33" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
+    <row r="34" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="E34" t="s">
-        <v>76</v>
-      </c>
-      <c r="F34" t="s">
+      <c r="E34" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F34" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
+    <row r="35" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="E35" t="s">
-        <v>76</v>
-      </c>
-      <c r="F35" t="s">
+      <c r="E35" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F35" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
+    <row r="36" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="E36" t="s">
-        <v>76</v>
-      </c>
-      <c r="F36" t="s">
+      <c r="E36" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F36" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
+    <row r="37" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E37" t="s">
-        <v>76</v>
-      </c>
-      <c r="F37" t="s">
+      <c r="E37" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F37" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
+    <row r="38" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E38" t="s">
-        <v>76</v>
-      </c>
-      <c r="F38" t="s">
+      <c r="E38" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F38" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
+    <row r="39" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E39" t="s">
-        <v>76</v>
-      </c>
-      <c r="F39" t="s">
+      <c r="E39" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F39" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
+    <row r="40" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E40" t="s">
-        <v>76</v>
-      </c>
-      <c r="F40" t="s">
+      <c r="E40" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F40" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
+    <row r="41" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E41" t="s">
-        <v>76</v>
-      </c>
-      <c r="F41" t="s">
+      <c r="E41" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F41" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
+    <row r="42" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E42" t="s">
-        <v>76</v>
-      </c>
-      <c r="F42" t="s">
+      <c r="E42" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F42" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
+    <row r="43" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E43" t="s">
-        <v>76</v>
-      </c>
-      <c r="F43" t="s">
+      <c r="E43" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F43" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
+    <row r="44" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E44" t="s">
-        <v>76</v>
-      </c>
-      <c r="F44" t="s">
+      <c r="E44" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F44" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
+    <row r="45" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="E45" t="s">
-        <v>76</v>
-      </c>
-      <c r="F45" t="s">
+      <c r="E45" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F45" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
+    <row r="46" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E46" t="s">
-        <v>76</v>
-      </c>
-      <c r="F46" t="s">
+      <c r="E46" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F46" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
+    <row r="47" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D47" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="E47" t="s">
-        <v>76</v>
-      </c>
-      <c r="F47" t="s">
+      <c r="E47" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F47" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
+    <row r="48" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="E48" t="s">
-        <v>76</v>
-      </c>
-      <c r="F48" t="s">
+      <c r="E48" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F48" s="4" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
+    <row r="49" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E49" t="s">
-        <v>76</v>
-      </c>
-      <c r="F49" t="s">
+      <c r="E49" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F49" s="4" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
+    <row r="50" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E50" t="s">
-        <v>76</v>
-      </c>
-      <c r="F50" t="s">
+      <c r="E50" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F50" s="4" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
+    <row r="51" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E51" t="s">
-        <v>76</v>
-      </c>
-      <c r="F51" t="s">
+      <c r="E51" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F51" s="4" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
+    <row r="52" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E52" t="s">
-        <v>76</v>
-      </c>
-      <c r="F52" t="s">
+      <c r="E52" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F52" s="4" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
+    <row r="53" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="E53" t="s">
-        <v>76</v>
-      </c>
-      <c r="F53" t="s">
+      <c r="E53" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F53" s="4" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
+    <row r="54" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="E54" t="s">
-        <v>76</v>
-      </c>
-      <c r="F54" t="s">
+      <c r="E54" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F54" s="4" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
+    <row r="55" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="E55" t="s">
-        <v>76</v>
-      </c>
-      <c r="F55" t="s">
+      <c r="E55" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F55" s="4" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
+    <row r="56" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="E56" t="s">
-        <v>76</v>
-      </c>
-      <c r="F56" t="s">
+      <c r="E56" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F56" s="4" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
+    <row r="57" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="E57" t="s">
-        <v>76</v>
-      </c>
-      <c r="F57" t="s">
+      <c r="E57" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F57" s="4" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
+    <row r="58" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="E58" t="s">
-        <v>76</v>
-      </c>
-      <c r="F58" t="s">
+      <c r="E58" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F58" s="4" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
+    <row r="59" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="E59" t="s">
-        <v>76</v>
-      </c>
-      <c r="F59" t="s">
+      <c r="E59" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F59" s="4" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
+    <row r="60" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="E60" t="s">
-        <v>76</v>
-      </c>
-      <c r="F60" t="s">
+      <c r="E60" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F60" s="4" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
+    <row r="61" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E61" t="s">
-        <v>76</v>
-      </c>
-      <c r="F61" t="s">
+      <c r="E61" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F61" s="4" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
+    <row r="62" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E62" t="s">
-        <v>76</v>
-      </c>
-      <c r="F62" t="s">
+      <c r="E62" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F62" s="4" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
+    <row r="63" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E63" t="s">
-        <v>76</v>
-      </c>
-      <c r="F63" t="s">
+      <c r="E63" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F63" s="4" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
+    <row r="64" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="E64" t="s">
-        <v>76</v>
-      </c>
-      <c r="F64" t="s">
+      <c r="E64" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F64" s="4" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
+    <row r="65" spans="1:6" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="E65" t="s">
-        <v>76</v>
-      </c>
-      <c r="F65" t="s">
+      <c r="E65" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F65" s="4" t="s">
         <v>130</v>
       </c>
     </row>
@@ -4051,1347 +4229,1350 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C122"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="35.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="35.1640625" style="2"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="2" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="3" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="4" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="5" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
+    <row r="6" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
+    <row r="7" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
+    <row r="8" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
+    <row r="9" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
+    <row r="10" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" t="s">
+    <row r="11" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" t="s">
+    <row r="12" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" t="s">
+    <row r="13" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" t="s">
+    <row r="14" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" t="s">
+    <row r="15" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" t="s">
+    <row r="16" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" t="s">
+    <row r="17" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" t="s">
+    <row r="18" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" t="s">
+    <row r="19" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" t="s">
+    <row r="20" spans="1:3" ht="80" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" t="s">
+    <row r="21" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" t="s">
+    <row r="22" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" t="s">
+    <row r="23" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" t="s">
+    <row r="24" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25" t="s">
+    <row r="25" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" t="s">
+    <row r="26" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>8</v>
-      </c>
-      <c r="B27" t="s">
+    <row r="27" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>8</v>
-      </c>
-      <c r="B28" t="s">
+    <row r="28" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>8</v>
-      </c>
-      <c r="B29" t="s">
+    <row r="29" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>8</v>
-      </c>
-      <c r="B30" t="s">
+    <row r="30" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>8</v>
-      </c>
-      <c r="B31" t="s">
+    <row r="31" spans="1:3" ht="80" x14ac:dyDescent="0.2">
+      <c r="A31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>8</v>
-      </c>
-      <c r="B32" t="s">
+    <row r="32" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>8</v>
-      </c>
-      <c r="B33" t="s">
+    <row r="33" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>8</v>
-      </c>
-      <c r="B34" t="s">
+    <row r="34" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>8</v>
-      </c>
-      <c r="B35" t="s">
+    <row r="35" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>8</v>
-      </c>
-      <c r="B36" t="s">
+    <row r="36" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>8</v>
-      </c>
-      <c r="B37" t="s">
+    <row r="37" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>8</v>
-      </c>
-      <c r="B38" t="s">
+    <row r="38" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>8</v>
-      </c>
-      <c r="B39" t="s">
+    <row r="39" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>8</v>
-      </c>
-      <c r="B40" t="s">
+    <row r="40" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>8</v>
-      </c>
-      <c r="B41" t="s">
+    <row r="41" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>8</v>
-      </c>
-      <c r="B42" t="s">
+    <row r="42" spans="1:3" ht="80" x14ac:dyDescent="0.2">
+      <c r="A42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>8</v>
-      </c>
-      <c r="B43" t="s">
+    <row r="43" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>8</v>
-      </c>
-      <c r="B44" t="s">
+    <row r="44" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>8</v>
-      </c>
-      <c r="B45" t="s">
+    <row r="45" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>8</v>
-      </c>
-      <c r="B46" t="s">
+    <row r="46" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>8</v>
-      </c>
-      <c r="B47" t="s">
+    <row r="47" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>8</v>
-      </c>
-      <c r="B48" t="s">
+    <row r="48" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>8</v>
-      </c>
-      <c r="B49" t="s">
+    <row r="49" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>8</v>
-      </c>
-      <c r="B50" t="s">
+    <row r="50" spans="1:3" ht="112" x14ac:dyDescent="0.2">
+      <c r="A50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="2" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>8</v>
-      </c>
-      <c r="B51" t="s">
+    <row r="51" spans="1:3" ht="112" x14ac:dyDescent="0.2">
+      <c r="A51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>8</v>
-      </c>
-      <c r="B52" t="s">
+    <row r="52" spans="1:3" ht="128" x14ac:dyDescent="0.2">
+      <c r="A52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>8</v>
-      </c>
-      <c r="B53" t="s">
+    <row r="53" spans="1:3" ht="128" x14ac:dyDescent="0.2">
+      <c r="A53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>8</v>
-      </c>
-      <c r="B54" t="s">
+    <row r="54" spans="1:3" ht="128" x14ac:dyDescent="0.2">
+      <c r="A54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>8</v>
-      </c>
-      <c r="B55" t="s">
+    <row r="55" spans="1:3" ht="128" x14ac:dyDescent="0.2">
+      <c r="A55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>8</v>
-      </c>
-      <c r="B56" t="s">
+    <row r="56" spans="1:3" ht="96" x14ac:dyDescent="0.2">
+      <c r="A56" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>8</v>
-      </c>
-      <c r="B57" t="s">
+    <row r="57" spans="1:3" ht="96" x14ac:dyDescent="0.2">
+      <c r="A57" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B57" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
+    <row r="58" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A58" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
+    <row r="59" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A59" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
+    <row r="60" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A60" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
+    <row r="61" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A61" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
+    <row r="62" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A62" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
+    <row r="63" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A63" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
+    <row r="64" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A64" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
+    <row r="65" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A65" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
+    <row r="66" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A66" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C66" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
+    <row r="67" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A67" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C67" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
+    <row r="68" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A68" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C68" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
+    <row r="69" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A69" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C69" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
+    <row r="70" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A70" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C70" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
+    <row r="71" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A71" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C71" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
+    <row r="72" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A72" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C72" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
+    <row r="73" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A73" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C73" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
+    <row r="74" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A74" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C74" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
+    <row r="75" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A75" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
+    <row r="76" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A76" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
+    <row r="77" spans="1:3" ht="128" x14ac:dyDescent="0.2">
+      <c r="A77" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C77" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
+    <row r="78" spans="1:3" ht="112" x14ac:dyDescent="0.2">
+      <c r="A78" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C78" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
+    <row r="79" spans="1:3" ht="80" x14ac:dyDescent="0.2">
+      <c r="A79" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C79" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A80" t="s">
+    <row r="80" spans="1:3" ht="80" x14ac:dyDescent="0.2">
+      <c r="A80" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C80" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A81" t="s">
+    <row r="81" spans="1:3" ht="80" x14ac:dyDescent="0.2">
+      <c r="A81" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C81" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A82" t="s">
+    <row r="82" spans="1:3" ht="128" x14ac:dyDescent="0.2">
+      <c r="A82" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C82" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A83" t="s">
+    <row r="83" spans="1:3" ht="128" x14ac:dyDescent="0.2">
+      <c r="A83" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C83" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A84" t="s">
+    <row r="84" spans="1:3" ht="128" x14ac:dyDescent="0.2">
+      <c r="A84" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C84" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A85" t="s">
+    <row r="85" spans="1:3" ht="128" x14ac:dyDescent="0.2">
+      <c r="A85" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C85" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A86" t="s">
+    <row r="86" spans="1:3" ht="96" x14ac:dyDescent="0.2">
+      <c r="A86" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C86" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A87" t="s">
+    <row r="87" spans="1:3" ht="96" x14ac:dyDescent="0.2">
+      <c r="A87" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C87" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A88" t="s">
+    <row r="88" spans="1:3" ht="112" x14ac:dyDescent="0.2">
+      <c r="A88" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C88" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A89" t="s">
+    <row r="89" spans="1:3" ht="112" x14ac:dyDescent="0.2">
+      <c r="A89" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C89" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A90" t="s">
+    <row r="90" spans="1:3" ht="112" x14ac:dyDescent="0.2">
+      <c r="A90" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C90" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A91" t="s">
+    <row r="91" spans="1:3" ht="112" x14ac:dyDescent="0.2">
+      <c r="A91" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C91" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A92" t="s">
+    <row r="92" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A92" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C92" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A93" t="s">
+    <row r="93" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A93" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C93" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A94" t="s">
+    <row r="94" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A94" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C94" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A95" t="s">
+    <row r="95" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A95" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C95" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A96" t="s">
+    <row r="96" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A96" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C96" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A97" t="s">
+    <row r="97" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A97" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C97" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A98" t="s">
+    <row r="98" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A98" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C98" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A99" t="s">
+    <row r="99" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A99" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="C99" t="s">
+      <c r="C99" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A100" t="s">
+    <row r="100" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A100" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C100" t="s">
+      <c r="C100" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A101" t="s">
+    <row r="101" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A101" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C101" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A102" t="s">
+    <row r="102" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A102" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C102" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A103" t="s">
+    <row r="103" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A103" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C103" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A104" t="s">
+    <row r="104" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A104" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C104" t="s">
+      <c r="C104" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A105" t="s">
+    <row r="105" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A105" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C105" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A106" t="s">
+    <row r="106" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A106" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C106" t="s">
+      <c r="C106" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A107" t="s">
+    <row r="107" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A107" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C107" t="s">
+      <c r="C107" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A108" t="s">
+    <row r="108" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A108" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C108" t="s">
+      <c r="C108" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A109" t="s">
+    <row r="109" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A109" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C109" t="s">
+      <c r="C109" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A110" t="s">
+    <row r="110" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A110" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="C110" t="s">
+      <c r="C110" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A111" t="s">
+    <row r="111" spans="1:3" ht="224" x14ac:dyDescent="0.2">
+      <c r="A111" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C111" t="s">
+      <c r="C111" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A112" t="s">
+    <row r="112" spans="1:3" ht="224" x14ac:dyDescent="0.2">
+      <c r="A112" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C112" t="s">
+      <c r="C112" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A113" t="s">
+    <row r="113" spans="1:3" ht="80" x14ac:dyDescent="0.2">
+      <c r="A113" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C113" t="s">
+      <c r="C113" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A114" t="s">
+    <row r="114" spans="1:3" ht="112" x14ac:dyDescent="0.2">
+      <c r="A114" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C114" t="s">
+      <c r="C114" s="2" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A115" t="s">
+    <row r="115" spans="1:3" ht="128" x14ac:dyDescent="0.2">
+      <c r="A115" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C115" t="s">
+      <c r="C115" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A116" t="s">
+    <row r="116" spans="1:3" ht="112" x14ac:dyDescent="0.2">
+      <c r="A116" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C116" t="s">
+      <c r="C116" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A117" t="s">
+    <row r="117" spans="1:3" ht="128" x14ac:dyDescent="0.2">
+      <c r="A117" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C117" t="s">
+      <c r="C117" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A118" t="s">
+    <row r="118" spans="1:3" ht="128" x14ac:dyDescent="0.2">
+      <c r="A118" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="C118" t="s">
+      <c r="C118" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A119" t="s">
+    <row r="119" spans="1:3" ht="128" x14ac:dyDescent="0.2">
+      <c r="A119" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C119" t="s">
+      <c r="C119" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A120" t="s">
+    <row r="120" spans="1:3" ht="128" x14ac:dyDescent="0.2">
+      <c r="A120" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C120" t="s">
+      <c r="C120" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A121" t="s">
+    <row r="121" spans="1:3" ht="96" x14ac:dyDescent="0.2">
+      <c r="A121" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="C121" t="s">
+      <c r="C121" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A122" t="s">
+    <row r="122" spans="1:3" ht="96" x14ac:dyDescent="0.2">
+      <c r="A122" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="C122" t="s">
+      <c r="C122" s="2" t="s">
         <v>107</v>
       </c>
     </row>
